--- a/islami-assistant-web/public/data/الاسئلة.xlsx
+++ b/islami-assistant-web/public/data/الاسئلة.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\islami-assistant-web\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3499C92-7FA6-4C6C-9BFA-B3EBB83F9999}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB597115-1D8A-4B06-822A-AFF0B7D041C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,15 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t xml:space="preserve">سؤال </t>
   </si>
   <si>
     <t>الجواب</t>
-  </si>
-  <si>
-    <t>صورة</t>
   </si>
   <si>
     <t xml:space="preserve">تفعيل التطبيق </t>
@@ -46,15 +44,30 @@
 4- من خلال خدمة البنك الناطق وتتم من خلال التواصل مع رقم مركز الاتصال 065680001 ويجب ان يكون مفعل مسبقا للدخول للبنك الناطق بالرقم السري الخاص بالبنك الناطق واختيار خيار تفعيل الخدمات الالكترونية 
 5- زيارة اقرب فرع للبنك الاسلامي ومن خلال موظف الخدمات الالكترونية او من موظف خدمة العملاء </t>
   </si>
+  <si>
+    <t xml:space="preserve">ابصر كيف حالك </t>
+  </si>
+  <si>
+    <t xml:space="preserve">من الله بخير من عباده لا </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كلمات مفتاحيه </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -68,7 +81,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -116,34 +129,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -156,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -167,13 +156,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -183,101 +166,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -288,17 +177,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D24CA1C1-38C0-4EF4-8EAC-B17DA2C7AD88}" name="Table1" displayName="Table1" ref="A1:C1048576" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EE38E9C0-B50D-46BB-8A82-982ADFC31C44}" name="سؤال " dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{71BB4AAD-1DB8-4D83-A03D-11FB4DB6B767}" name="الجواب" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{B706CC58-8F39-4C68-A9CE-1D9081578A04}" name="صورة" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,12 +442,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" style="4" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="6"/>
+    <col min="1" max="1" width="11" style="3" customWidth="1"/>
+    <col min="2" max="3" width="36.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -579,23 +456,32 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="405" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>